--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.104.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.104.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.104.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.104.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ï»¿THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE MASTER’S OFFICE.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE MASTER’S OFFICE.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L40: symbol-only separator/garbage line :: (56).</t>
@@ -669,7 +673,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -687,11 +691,7 @@
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: either upon written interrogatories, or viva vocÃ¨, or in other person</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -746,11 +746,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s office, it</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -783,7 +779,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -841,7 +837,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -998,7 +994,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1041,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
